--- a/data/dNdSDistCorr.xlsx
+++ b/data/dNdSDistCorr.xlsx
@@ -1319,46 +1319,46 @@
         <v>43</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.5716011632419762</v>
+        <v>-0.5761316876534053</v>
       </c>
       <c r="D20" t="n">
-        <v>6.23546554893122e-05</v>
+        <v>5.282188895954777e-05</v>
       </c>
       <c r="E20" t="n">
         <v>43</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3486238534594721</v>
+        <v>0.3446973989695669</v>
       </c>
       <c r="G20" t="n">
-        <v>0.02195657659617945</v>
+        <v>0.02359896624308797</v>
       </c>
       <c r="H20" t="n">
         <v>43</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.01812209764571655</v>
+        <v>-0.05542341529981644</v>
       </c>
       <c r="J20" t="n">
-        <v>0.908173885735802</v>
+        <v>0.7240901108594137</v>
       </c>
       <c r="K20" t="n">
         <v>43</v>
       </c>
       <c r="L20" t="n">
-        <v>0.2192018727729798</v>
+        <v>0.2204100126160275</v>
       </c>
       <c r="M20" t="n">
-        <v>0.1578646939259604</v>
+        <v>0.1555289607026694</v>
       </c>
       <c r="N20" t="n">
         <v>43</v>
       </c>
       <c r="O20" t="n">
-        <v>0.4279347479521331</v>
+        <v>0.435544402868464</v>
       </c>
       <c r="P20" t="n">
-        <v>0.004202021743980388</v>
+        <v>0.003509477379682907</v>
       </c>
     </row>
     <row r="21">
@@ -1371,46 +1371,46 @@
         <v>43</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.4065237088492902</v>
+        <v>-0.4237390516460284</v>
       </c>
       <c r="D21" t="n">
-        <v>0.006827849107082867</v>
+        <v>0.004632694442913084</v>
       </c>
       <c r="E21" t="n">
         <v>43</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2713681667170039</v>
+        <v>0.2769556025369979</v>
       </c>
       <c r="G21" t="n">
-        <v>0.07836688782167993</v>
+        <v>0.07218387884554965</v>
       </c>
       <c r="H21" t="n">
         <v>43</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2233464210208397</v>
+        <v>-0.2684989429175476</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1499573777209659</v>
+        <v>0.08169928328348891</v>
       </c>
       <c r="K21" t="n">
         <v>43</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1892177589852008</v>
+        <v>0.1942011476895198</v>
       </c>
       <c r="M21" t="n">
-        <v>0.2242760587692088</v>
+        <v>0.212083212254077</v>
       </c>
       <c r="N21" t="n">
         <v>43</v>
       </c>
       <c r="O21" t="n">
-        <v>0.4039799002527935</v>
+        <v>0.3437948132649364</v>
       </c>
       <c r="P21" t="n">
-        <v>0.007218604389891518</v>
+        <v>0.02399067080572161</v>
       </c>
     </row>
     <row r="22">
@@ -1423,46 +1423,46 @@
         <v>64</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.1511446886446886</v>
+        <v>-0.1416208791208791</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2331869473412791</v>
+        <v>0.2643046320061039</v>
       </c>
       <c r="E22" t="n">
         <v>64</v>
       </c>
       <c r="F22" t="n">
-        <v>0.145054945054945</v>
+        <v>0.1356684981684982</v>
       </c>
       <c r="G22" t="n">
-        <v>0.2527775120239741</v>
+        <v>0.2851110680185955</v>
       </c>
       <c r="H22" t="n">
         <v>64</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.01991758241758242</v>
+        <v>-0.02426739926739927</v>
       </c>
       <c r="J22" t="n">
-        <v>0.8758630543990713</v>
+        <v>0.8490420428307613</v>
       </c>
       <c r="K22" t="n">
         <v>64</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.04239926739926739</v>
+        <v>-0.03704212454212454</v>
       </c>
       <c r="M22" t="n">
-        <v>0.739392047621096</v>
+        <v>0.7713601907242732</v>
       </c>
       <c r="N22" t="n">
         <v>64</v>
       </c>
       <c r="O22" t="n">
-        <v>0.3122886285898264</v>
+        <v>0.3146822684359379</v>
       </c>
       <c r="P22" t="n">
-        <v>0.01199660637418314</v>
+        <v>0.01132404690294524</v>
       </c>
     </row>
     <row r="23">
@@ -1475,46 +1475,46 @@
         <v>64</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.10503663003663</v>
+        <v>-0.09894688644688643</v>
       </c>
       <c r="D23" t="n">
-        <v>0.4087927632641611</v>
+        <v>0.4366365302245099</v>
       </c>
       <c r="E23" t="n">
         <v>64</v>
       </c>
       <c r="F23" t="n">
-        <v>0.4543040293040292</v>
+        <v>0.459569597069597</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0001626852195888509</v>
+        <v>0.0001333690994533209</v>
       </c>
       <c r="H23" t="n">
         <v>64</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.1108974358974359</v>
+        <v>-0.1146520146520146</v>
       </c>
       <c r="J23" t="n">
-        <v>0.3829961609482735</v>
+        <v>0.3669940662635867</v>
       </c>
       <c r="K23" t="n">
         <v>64</v>
       </c>
       <c r="L23" t="n">
-        <v>0.3013736263736263</v>
+        <v>0.3060897435897435</v>
       </c>
       <c r="M23" t="n">
-        <v>0.0155193551894686</v>
+        <v>0.01390110691291931</v>
       </c>
       <c r="N23" t="n">
         <v>64</v>
       </c>
       <c r="O23" t="n">
-        <v>0.1787591682063037</v>
+        <v>0.1787131259221552</v>
       </c>
       <c r="P23" t="n">
-        <v>0.157567506215448</v>
+        <v>0.1576762791782796</v>
       </c>
     </row>
     <row r="25">
@@ -2314,46 +2314,46 @@
         <v>39</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.6214574898785425</v>
+        <v>-0.6273279352226722</v>
       </c>
       <c r="D41" t="n">
-        <v>2.418914084855971e-05</v>
+        <v>1.920678983940553e-05</v>
       </c>
       <c r="E41" t="n">
         <v>39</v>
       </c>
       <c r="F41" t="n">
-        <v>0.2748987854251013</v>
+        <v>0.2704453441295547</v>
       </c>
       <c r="G41" t="n">
-        <v>0.09032367676947162</v>
+        <v>0.09587815965610745</v>
       </c>
       <c r="H41" t="n">
         <v>39</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.1196356275303644</v>
+        <v>-0.1544534412955466</v>
       </c>
       <c r="J41" t="n">
-        <v>0.4681895890256537</v>
+        <v>0.347818424994229</v>
       </c>
       <c r="K41" t="n">
         <v>39</v>
       </c>
       <c r="L41" t="n">
-        <v>0.1831983805668016</v>
+        <v>0.1846153846153847</v>
       </c>
       <c r="M41" t="n">
-        <v>0.2642806784028036</v>
+        <v>0.2605397429662586</v>
       </c>
       <c r="N41" t="n">
         <v>39</v>
       </c>
       <c r="O41" t="n">
-        <v>0.4008664825834045</v>
+        <v>0.4102080358369921</v>
       </c>
       <c r="P41" t="n">
-        <v>0.01143815489062815</v>
+        <v>0.009495874831884981</v>
       </c>
     </row>
     <row r="42">
@@ -2366,46 +2366,46 @@
         <v>39</v>
       </c>
       <c r="C42" t="n">
-        <v>-0.4477732793522268</v>
+        <v>-0.4686234817813765</v>
       </c>
       <c r="D42" t="n">
-        <v>0.004257832144848311</v>
+        <v>0.002621341195041851</v>
       </c>
       <c r="E42" t="n">
         <v>39</v>
       </c>
       <c r="F42" t="n">
-        <v>0.2597165991902834</v>
+        <v>0.2663967611336032</v>
       </c>
       <c r="G42" t="n">
-        <v>0.1103337112428837</v>
+        <v>0.1011517768014986</v>
       </c>
       <c r="H42" t="n">
         <v>39</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.2682186234817814</v>
+        <v>-0.3208502024291499</v>
       </c>
       <c r="J42" t="n">
-        <v>0.09875189028100417</v>
+        <v>0.04642385320503102</v>
       </c>
       <c r="K42" t="n">
         <v>39</v>
       </c>
       <c r="L42" t="n">
-        <v>0.2060728744939271</v>
+        <v>0.2121457489878543</v>
       </c>
       <c r="M42" t="n">
-        <v>0.2081695428241836</v>
+        <v>0.1947820550734695</v>
       </c>
       <c r="N42" t="n">
         <v>39</v>
       </c>
       <c r="O42" t="n">
-        <v>0.409907866086935</v>
+        <v>0.3435210162074219</v>
       </c>
       <c r="P42" t="n">
-        <v>0.009553589295936306</v>
+        <v>0.03226387265584817</v>
       </c>
     </row>
     <row r="43">
@@ -2418,46 +2418,46 @@
         <v>51</v>
       </c>
       <c r="C43" t="n">
-        <v>-0.100814479638009</v>
+        <v>-0.09266968325791854</v>
       </c>
       <c r="D43" t="n">
-        <v>0.4814905547921191</v>
+        <v>0.5177735103300314</v>
       </c>
       <c r="E43" t="n">
         <v>51</v>
       </c>
       <c r="F43" t="n">
-        <v>0.01746606334841629</v>
+        <v>-0.01737556561085973</v>
       </c>
       <c r="G43" t="n">
-        <v>0.9031765446288552</v>
+        <v>0.9036758455538464</v>
       </c>
       <c r="H43" t="n">
         <v>51</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.004072398190045248</v>
+        <v>-0.02579185520361991</v>
       </c>
       <c r="J43" t="n">
-        <v>0.9773735570093557</v>
+        <v>0.857424057158172</v>
       </c>
       <c r="K43" t="n">
         <v>51</v>
       </c>
       <c r="L43" t="n">
-        <v>-0.1388235294117647</v>
+        <v>-0.1656108597285068</v>
       </c>
       <c r="M43" t="n">
-        <v>0.3312818298344669</v>
+        <v>0.2454716298778674</v>
       </c>
       <c r="N43" t="n">
         <v>51</v>
       </c>
       <c r="O43" t="n">
-        <v>0.2317446949957741</v>
+        <v>0.2420246009087163</v>
       </c>
       <c r="P43" t="n">
-        <v>0.1017725334633554</v>
+        <v>0.08706375118312641</v>
       </c>
     </row>
     <row r="44">
@@ -2470,37 +2470,37 @@
         <v>51</v>
       </c>
       <c r="C44" t="n">
-        <v>-0.04479638009049773</v>
+        <v>-0.04226244343891403</v>
       </c>
       <c r="D44" t="n">
-        <v>0.7549372232750036</v>
+        <v>0.7684037809515716</v>
       </c>
       <c r="E44" t="n">
         <v>51</v>
       </c>
       <c r="F44" t="n">
-        <v>0.4409954751131221</v>
+        <v>0.4460633484162895</v>
       </c>
       <c r="G44" t="n">
-        <v>0.001199388761705041</v>
+        <v>0.001035588287981267</v>
       </c>
       <c r="H44" t="n">
         <v>51</v>
       </c>
       <c r="I44" t="n">
-        <v>0.05873303167420814</v>
+        <v>0.0588235294117647</v>
       </c>
       <c r="J44" t="n">
-        <v>0.6822511874311757</v>
+        <v>0.6817875923296997</v>
       </c>
       <c r="K44" t="n">
         <v>51</v>
       </c>
       <c r="L44" t="n">
-        <v>0.3006334841628959</v>
+        <v>0.3028959276018099</v>
       </c>
       <c r="M44" t="n">
-        <v>0.03206592273453993</v>
+        <v>0.03073248476200006</v>
       </c>
       <c r="N44" t="n">
         <v>51</v>
@@ -3413,46 +3413,46 @@
         <v>40</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.07185741088180113</v>
+        <v>-0.06810506566604127</v>
       </c>
       <c r="D64" t="n">
-        <v>0.6594841815382813</v>
+        <v>0.6762680398344609</v>
       </c>
       <c r="E64" t="n">
         <v>40</v>
       </c>
       <c r="F64" t="n">
-        <v>0.401500938086304</v>
+        <v>0.3915572232645404</v>
       </c>
       <c r="G64" t="n">
-        <v>0.01023305886876121</v>
+        <v>0.01246995493577225</v>
       </c>
       <c r="H64" t="n">
         <v>40</v>
       </c>
       <c r="I64" t="n">
-        <v>0.176360225140713</v>
+        <v>0.1621013133208256</v>
       </c>
       <c r="J64" t="n">
-        <v>0.2763342778107473</v>
+        <v>0.3176307716641729</v>
       </c>
       <c r="K64" t="n">
         <v>40</v>
       </c>
       <c r="L64" t="n">
-        <v>0.1195121951219512</v>
+        <v>0.1294559099437148</v>
       </c>
       <c r="M64" t="n">
-        <v>0.4626245816795939</v>
+        <v>0.4259465730563532</v>
       </c>
       <c r="N64" t="n">
         <v>40</v>
       </c>
       <c r="O64" t="n">
-        <v>0.5242081069297413</v>
+        <v>0.5294301033972406</v>
       </c>
       <c r="P64" t="n">
-        <v>0.000516784741935366</v>
+        <v>0.0004433715302118059</v>
       </c>
     </row>
     <row r="65">
